--- a/fix-errors/ig/FRObservationMultiresistantMicroorganismsIdentificationLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRObservationMultiresistantMicroorganismsIdentificationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-multidrug-resistant-microorganism-identification</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-multidrug-resistant-microorganism-identification|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-identification-micro-organismes-multiresistants</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-identification-micro-organismes-multiresistants|0.1.0</t>
   </si>
   <si>
     <t>FRLMMultidrugResistantMicroorganismIdentification</t>
@@ -190,10 +190,10 @@
     <t>FRCDAIdentificationMicroOrganismesMultiresistants.value</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-ml-multidrug-resistant-microorganism-identification</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-multiresistant-microorganism-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-ml-multidrug-resistant-microorganism-identification</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-multiresistant-microorganism-document|0.1.0</t>
   </si>
   <si>
     <t>FRObservationMultidrugResistantMicroorganismIdentification</t>
